--- a/data/db/cmv/resistances.xlsx
+++ b/data/db/cmv/resistances.xlsx
@@ -5,23 +5,23 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="resistances" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="metadata" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t xml:space="preserve">CHROM</t>
   </si>
@@ -62,6 +62,15 @@
     <t xml:space="preserve">aa_position_offset</t>
   </si>
   <si>
+    <t xml:space="preserve">hgvs_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hgvs_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hgvs_note</t>
+  </si>
+  <si>
     <t xml:space="preserve">NA</t>
   </si>
   <si>
@@ -81,15 +90,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;VERDADERO&quot;;&quot;VERDADERO&quot;;&quot;FALSO&quot;"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="0\ %"/>
+    <numFmt numFmtId="170" formatCode="&quot;VERDADERO&quot;;&quot;VERDADERO&quot;;&quot;FALSO&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -110,13 +123,20 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -159,7 +179,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -183,60 +203,85 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="20"/>
+    <cellStyle name="Comma [0]" xfId="21"/>
+    <cellStyle name="Currency" xfId="22"/>
+    <cellStyle name="Currency [0]" xfId="23"/>
+    <cellStyle name="Normal" xfId="24"/>
+    <cellStyle name="Percent" xfId="25"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -307,12 +352,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AL804"/>
-  <sheetFormatPr defaultColWidth="10.4296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="15.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="21.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="19.6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -355,50 +408,65 @@
       <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -3502,7 +3570,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3516,22 +3584,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3544,11 +3612,11 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>